--- a/outputs/M2_main_monetary_policy_regression_detail.xlsx
+++ b/outputs/M2_main_monetary_policy_regression_detail.xlsx
@@ -40,22 +40,22 @@
     <t>Intercept</t>
   </si>
   <si>
+    <t>inflation_gdp_deflator_pct</t>
+  </si>
+  <si>
+    <t>trade_pct_gdp</t>
+  </si>
+  <si>
+    <t>ln_gdppc</t>
+  </si>
+  <si>
+    <t>xr_dep_pct</t>
+  </si>
+  <si>
     <t>broad_money_pct_gdp</t>
   </si>
   <si>
     <t>deposit_interest_rate_pct</t>
-  </si>
-  <si>
-    <t>inflation_gdp_deflator_pct</t>
-  </si>
-  <si>
-    <t>trade_pct_gdp</t>
-  </si>
-  <si>
-    <t>ln_gdppc</t>
-  </si>
-  <si>
-    <t>xr_dep_pct</t>
   </si>
 </sst>
 </file>
@@ -447,19 +447,19 @@
         <v>34.166060672908</v>
       </c>
       <c r="C2">
-        <v>30.81798693449519</v>
+        <v>30.81798693451466</v>
       </c>
       <c r="D2">
-        <v>1.108640247837384</v>
+        <v>1.108640247836683</v>
       </c>
       <c r="E2">
-        <v>0.271379959105198</v>
+        <v>0.2713799591054977</v>
       </c>
       <c r="F2">
-        <v>-27.29847617932874</v>
+        <v>-27.29847617936757</v>
       </c>
       <c r="G2">
-        <v>95.63059752514474</v>
+        <v>95.63059752518357</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -467,22 +467,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.07315701189152647</v>
+        <v>0.03568166288154202</v>
       </c>
       <c r="C3">
-        <v>0.07857878424469744</v>
+        <v>0.09357740648885951</v>
       </c>
       <c r="D3">
-        <v>0.9310020840194301</v>
+        <v>0.3813063881588763</v>
       </c>
       <c r="E3">
-        <v>0.3550523101613041</v>
+        <v>0.7041308384634848</v>
       </c>
       <c r="F3">
-        <v>-0.08356343160395908</v>
+        <v>-0.1509525894431372</v>
       </c>
       <c r="G3">
-        <v>0.229877455387012</v>
+        <v>0.2223159152062212</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -490,22 +490,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>-0.294022774251117</v>
+        <v>-0.03805207816704496</v>
       </c>
       <c r="C4">
-        <v>0.3102019901436653</v>
+        <v>0.02242993836246056</v>
       </c>
       <c r="D4">
-        <v>-0.9478429655301208</v>
+        <v>-1.69648607821099</v>
       </c>
       <c r="E4">
-        <v>0.346470177984417</v>
+        <v>0.09423690921082928</v>
       </c>
       <c r="F4">
-        <v>-0.9127011355389227</v>
+        <v>-0.08278717965187654</v>
       </c>
       <c r="G4">
-        <v>0.3246555870366887</v>
+        <v>0.006683023317786613</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -513,22 +513,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.035681662881542</v>
+        <v>-3.509735229505306</v>
       </c>
       <c r="C5">
-        <v>0.09357740648884863</v>
+        <v>3.868538185197572</v>
       </c>
       <c r="D5">
-        <v>0.3813063881589204</v>
+        <v>-0.9072510238970432</v>
       </c>
       <c r="E5">
-        <v>0.7041308384634521</v>
+        <v>0.3673867464216936</v>
       </c>
       <c r="F5">
-        <v>-0.1509525894431155</v>
+        <v>-11.2252913543673</v>
       </c>
       <c r="G5">
-        <v>0.2223159152061995</v>
+        <v>4.205820895356685</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -536,22 +536,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>-0.03805207816704489</v>
+        <v>0.0508136944699662</v>
       </c>
       <c r="C6">
-        <v>0.02242993836245899</v>
+        <v>0.1011880237264107</v>
       </c>
       <c r="D6">
-        <v>-1.696486078211106</v>
+        <v>0.502171033672471</v>
       </c>
       <c r="E6">
-        <v>0.09423690921080707</v>
+        <v>0.6171232516817149</v>
       </c>
       <c r="F6">
-        <v>-0.08278717965187334</v>
+        <v>-0.1509994553167707</v>
       </c>
       <c r="G6">
-        <v>0.006683023317783546</v>
+        <v>0.2526268442567031</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -559,22 +559,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>-3.509735229505306</v>
+        <v>0.0731570118915265</v>
       </c>
       <c r="C7">
-        <v>3.868538185195457</v>
+        <v>0.07857878424469789</v>
       </c>
       <c r="D7">
-        <v>-0.9072510238975391</v>
+        <v>0.9310020840194251</v>
       </c>
       <c r="E7">
-        <v>0.3673867464214333</v>
+        <v>0.3550523101613066</v>
       </c>
       <c r="F7">
-        <v>-11.22529135436308</v>
+        <v>-0.08356343160395995</v>
       </c>
       <c r="G7">
-        <v>4.205820895352467</v>
+        <v>0.2298774553870129</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -582,22 +582,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.05081369446996623</v>
+        <v>-0.2940227742511168</v>
       </c>
       <c r="C8">
-        <v>0.1011880237264057</v>
+        <v>0.3102019901437114</v>
       </c>
       <c r="D8">
-        <v>0.5021710336724965</v>
+        <v>-0.9478429655299793</v>
       </c>
       <c r="E8">
-        <v>0.6171232516816967</v>
+        <v>0.3464701779844885</v>
       </c>
       <c r="F8">
-        <v>-0.1509994553167605</v>
+        <v>-0.9127011355390147</v>
       </c>
       <c r="G8">
-        <v>0.252626844256693</v>
+        <v>0.3246555870367809</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/M2_main_monetary_policy_regression_detail.xlsx
+++ b/outputs/M2_main_monetary_policy_regression_detail.xlsx
@@ -40,6 +40,12 @@
     <t>Intercept</t>
   </si>
   <si>
+    <t>broad_money_growth_pct</t>
+  </si>
+  <si>
+    <t>deposit_interest_rate_pct</t>
+  </si>
+  <si>
     <t>inflation_gdp_deflator_pct</t>
   </si>
   <si>
@@ -50,12 +56,6 @@
   </si>
   <si>
     <t>xr_dep_pct</t>
-  </si>
-  <si>
-    <t>broad_money_pct_gdp</t>
-  </si>
-  <si>
-    <t>deposit_interest_rate_pct</t>
   </si>
 </sst>
 </file>
@@ -444,22 +444,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>34.166060672908</v>
+        <v>-18.56533987073459</v>
       </c>
       <c r="C2">
-        <v>30.81798693451466</v>
+        <v>13.60577948410195</v>
       </c>
       <c r="D2">
-        <v>1.108640247836683</v>
+        <v>-1.364518651241391</v>
       </c>
       <c r="E2">
-        <v>0.2713799591054977</v>
+        <v>0.1750918600514613</v>
       </c>
       <c r="F2">
-        <v>-27.29847617936757</v>
+        <v>-45.51828423617669</v>
       </c>
       <c r="G2">
-        <v>95.63059752518357</v>
+        <v>8.387604494707517</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -467,22 +467,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.03568166288154202</v>
+        <v>0.04510828943104767</v>
       </c>
       <c r="C3">
-        <v>0.09357740648885951</v>
+        <v>0.03876528693280604</v>
       </c>
       <c r="D3">
-        <v>0.3813063881588763</v>
+        <v>1.16362583641484</v>
       </c>
       <c r="E3">
-        <v>0.7041308384634848</v>
+        <v>0.2470053771153966</v>
       </c>
       <c r="F3">
-        <v>-0.1509525894431372</v>
+        <v>-0.03168544541017854</v>
       </c>
       <c r="G3">
-        <v>0.2223159152062212</v>
+        <v>0.1219020242722739</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -490,22 +490,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>-0.03805207816704496</v>
+        <v>0.09223952245660531</v>
       </c>
       <c r="C4">
-        <v>0.02242993836246056</v>
+        <v>0.1241740158784403</v>
       </c>
       <c r="D4">
-        <v>-1.69648607821099</v>
+        <v>0.7428246707177681</v>
       </c>
       <c r="E4">
-        <v>0.09423690921082928</v>
+        <v>0.4591158093871686</v>
       </c>
       <c r="F4">
-        <v>-0.08278717965187654</v>
+        <v>-0.1537482466025545</v>
       </c>
       <c r="G4">
-        <v>0.006683023317786613</v>
+        <v>0.3382272915157651</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -513,22 +513,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>-3.509735229505306</v>
+        <v>0.001701189631536873</v>
       </c>
       <c r="C5">
-        <v>3.868538185197572</v>
+        <v>0.04407621384566034</v>
       </c>
       <c r="D5">
-        <v>-0.9072510238970432</v>
+        <v>0.03859654637065358</v>
       </c>
       <c r="E5">
-        <v>0.3673867464216936</v>
+        <v>0.969279565282132</v>
       </c>
       <c r="F5">
-        <v>-11.2252913543673</v>
+        <v>-0.08561345051896274</v>
       </c>
       <c r="G5">
-        <v>4.205820895356685</v>
+        <v>0.08901582978203648</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -536,22 +536,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.0508136944699662</v>
+        <v>-0.0153965368811574</v>
       </c>
       <c r="C6">
-        <v>0.1011880237264107</v>
+        <v>0.01747640025252997</v>
       </c>
       <c r="D6">
-        <v>0.502171033672471</v>
+        <v>-0.880990172957873</v>
       </c>
       <c r="E6">
-        <v>0.6171232516817149</v>
+        <v>0.3801767452120721</v>
       </c>
       <c r="F6">
-        <v>-0.1509994553167707</v>
+        <v>-0.05001715117709236</v>
       </c>
       <c r="G6">
-        <v>0.2526268442567031</v>
+        <v>0.01922407741477757</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -559,22 +559,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.0731570118915265</v>
+        <v>0.9641608184679905</v>
       </c>
       <c r="C7">
-        <v>0.07857878424469789</v>
+        <v>0.5559876424940187</v>
       </c>
       <c r="D7">
-        <v>0.9310020840194251</v>
+        <v>1.734140734033244</v>
       </c>
       <c r="E7">
-        <v>0.3550523101613066</v>
+        <v>0.08559632462762967</v>
       </c>
       <c r="F7">
-        <v>-0.08356343160395995</v>
+        <v>-0.1372464190610924</v>
       </c>
       <c r="G7">
-        <v>0.2298774553870129</v>
+        <v>2.065568055997073</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -582,22 +582,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>-0.2940227742511168</v>
+        <v>0.05388979153232129</v>
       </c>
       <c r="C8">
-        <v>0.3102019901437114</v>
+        <v>0.04131943335027024</v>
       </c>
       <c r="D8">
-        <v>-0.9478429655299793</v>
+        <v>1.304223876341442</v>
       </c>
       <c r="E8">
-        <v>0.3464701779844885</v>
+        <v>0.1947844009546209</v>
       </c>
       <c r="F8">
-        <v>-0.9127011355390147</v>
+        <v>-0.02796368768970618</v>
       </c>
       <c r="G8">
-        <v>0.3246555870367809</v>
+        <v>0.1357432707543488</v>
       </c>
     </row>
   </sheetData>
